--- a/assets/20260419UseCaseCert&CredMgmtReqs.xlsx
+++ b/assets/20260419UseCaseCert&CredMgmtReqs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adloffice365-my.sharepoint.com/personal/dawn_riddle_ctr_adlnet_gov/Documents/Documents/00-A_NEW/Use Cases _ Reqs/CertMgmt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66112E25-930D-418A-A998-FB278FD47BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DDE8EE4-DFAC-476F-B3D7-801A57F9BE3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="255" yWindow="315" windowWidth="27315" windowHeight="13845" firstSheet="1" activeTab="1" xr2:uid="{C84AAC64-F5A3-456B-84C5-F8C4DD4407E9}"/>
   </bookViews>
@@ -3340,6 +3340,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Record" ma:contentTypeID="0x010100D59BD9E0F6DE774A8E59AA9F2D5B6510" ma:contentTypeVersion="37" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a622c0d350f0df8de14f129e9dd2206d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="46ca075c-2170-40c9-9b1a-050a5cf91ade" xmlns:ns3="701e3041-6663-42cf-bcb1-1f646b56d146" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="399d4b3cd23da1aabd8988ac4d93dba4" ns2:_="" ns3:_="">
     <xsd:import namespace="46ca075c-2170-40c9-9b1a-050a5cf91ade"/>
@@ -3704,7 +3713,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Vital_x0020_Record xmlns="46ca075c-2170-40c9-9b1a-050a5cf91ade">false</Vital_x0020_Record>
@@ -3730,23 +3739,14 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E327052A-FDF4-4C12-B700-F480EEBE88C6}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{476C6CB6-2456-467C-8AC5-CE7A29DC43F2}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD38F168-25B8-482A-A49A-FD5C0A3CC636}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E327052A-FDF4-4C12-B700-F480EEBE88C6}"/>
 </file>